--- a/Pruebas calificadas/COLEGIO VEINTE DE JULIO-302_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO VEINTE DE JULIO-302_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -950,11 +946,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -1153,11 +1145,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -1356,11 +1344,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -1559,11 +1543,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -1762,11 +1742,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -1965,11 +1941,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -2168,11 +2140,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -2371,11 +2339,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -2574,11 +2538,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -2777,11 +2737,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -2980,11 +2936,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -3183,11 +3135,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -3386,11 +3334,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -3589,11 +3533,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -3792,11 +3732,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -3995,11 +3931,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -4194,11 +4126,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -4393,11 +4321,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -4596,11 +4520,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -4799,11 +4719,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -5002,11 +4918,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -5197,11 +5109,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -5400,11 +5308,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -5603,11 +5507,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -5806,11 +5706,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -6009,11 +5905,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -6212,11 +6104,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -6415,11 +6303,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -6618,11 +6502,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -6821,11 +6701,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -7024,11 +6900,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -7227,11 +7099,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -7430,11 +7298,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -7633,11 +7497,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -7836,11 +7696,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -8039,11 +7895,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -8242,11 +8094,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
